--- a/Data/Export/Common/JobType_指令.xlsx
+++ b/Data/Export/Common/JobType_指令.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175AC5CD-5F06-42FE-8458-FFF5BD4053F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5A5670-AA24-4D71-9CFE-9B1B10F46F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JobTypes" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="95">
   <si>
     <t>0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -354,6 +354,41 @@
   </si>
   <si>
     <t>外交/同盟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -819,23 +854,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:K102"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
-    <col min="2" max="2" width="5.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.7265625" style="2" customWidth="1"/>
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>1</v>
@@ -866,7 +901,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -881,7 +916,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -916,7 +951,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -951,7 +986,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -971,7 +1006,7 @@
         <v>56</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>13</v>
@@ -983,7 +1018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1004,7 +1039,7 @@
         <v>56</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>13</v>
@@ -1016,7 +1051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1036,10 +1071,10 @@
         <v>57</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="J7" s="4">
         <v>3</v>
@@ -1048,7 +1083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -1068,10 +1103,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="J8" s="4">
         <v>3</v>
@@ -1080,7 +1115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -1100,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>54</v>
@@ -1112,7 +1147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -1132,7 +1167,7 @@
         <v>59</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>54</v>
@@ -1144,7 +1179,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -1164,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>54</v>
@@ -1176,7 +1211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -1196,7 +1231,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>54</v>
@@ -1208,7 +1243,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -1228,10 +1263,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="J13" s="4">
         <v>3</v>
@@ -1240,7 +1275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -1260,10 +1295,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="J14" s="4">
         <v>3</v>
@@ -1272,7 +1307,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -1292,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="J15" s="4">
         <v>3</v>
@@ -1304,7 +1339,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -1324,10 +1359,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="J16" s="4">
         <v>3</v>
@@ -1336,7 +1371,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -1356,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>54</v>
@@ -1368,7 +1403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -1388,10 +1423,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="J18" s="4">
         <v>0</v>
@@ -1400,7 +1435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -1420,10 +1455,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="J19" s="4">
         <v>0</v>
@@ -1432,7 +1467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -1452,10 +1487,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="J20" s="4">
         <v>3</v>
@@ -1464,7 +1499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>17</v>
       </c>
@@ -1484,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>54</v>
@@ -1496,7 +1531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -1516,7 +1551,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>54</v>
@@ -1528,7 +1563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -1548,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>54</v>
@@ -1560,7 +1595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -1580,7 +1615,7 @@
         <v>57</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>54</v>
@@ -1592,7 +1627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -1612,7 +1647,7 @@
         <v>57</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>54</v>
@@ -1624,7 +1659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -1644,7 +1679,7 @@
         <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>54</v>
@@ -1656,7 +1691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -1676,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>13</v>
@@ -1688,337 +1723,363 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="J28" s="4"/>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B28" s="4">
+        <v>23</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="4">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="J30" s="4"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="J31" s="4"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="J32" s="4"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="J69" s="4"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="J70" s="4"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="J71" s="4"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="J72" s="4"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="J73" s="4"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
       <c r="J74" s="4"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="J75" s="4"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="J76" s="4"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="J77" s="4"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="J78" s="4"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="J79" s="4"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="J80" s="4"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="J81" s="4"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="J82" s="4"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="J83" s="4"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="J84" s="4"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="J85" s="4"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
       <c r="J86" s="4"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="J87" s="4"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="J88" s="4"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="J89" s="4"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="J90" s="4"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="J91" s="4"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="J92" s="4"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="4"/>
       <c r="J93" s="4"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="J94" s="4"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="J95" s="4"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="J96" s="4"/>
     </row>
-    <row r="97" spans="10:10" x14ac:dyDescent="0.15">
+    <row r="97" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J97" s="4"/>
     </row>
-    <row r="98" spans="10:10" x14ac:dyDescent="0.15">
+    <row r="98" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J98" s="4"/>
     </row>
-    <row r="99" spans="10:10" x14ac:dyDescent="0.15">
+    <row r="99" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J99" s="4"/>
     </row>
-    <row r="100" spans="10:10" x14ac:dyDescent="0.15">
+    <row r="100" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J100" s="4"/>
     </row>
-    <row r="101" spans="10:10" x14ac:dyDescent="0.15">
+    <row r="101" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J101" s="4"/>
     </row>
-    <row r="102" spans="10:10" x14ac:dyDescent="0.15">
+    <row r="102" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J102" s="4"/>
     </row>
   </sheetData>

--- a/Data/Export/Common/JobType_指令.xlsx
+++ b/Data/Export/Common/JobType_指令.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5A5670-AA24-4D71-9CFE-9B1B10F46F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203A42BB-D51D-41DD-9497-F98CDE16BB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JobTypes" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="95">
   <si>
     <t>0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -854,23 +854,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:K102"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
-    <col min="2" max="2" width="5.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.75" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.75" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.7265625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.75" style="2" customWidth="1"/>
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -916,7 +916,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -951,7 +951,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -986,7 +986,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1051,7 +1051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>17</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -1723,363 +1723,336 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="4">
-        <v>23</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J28" s="4">
-        <v>1</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="J30" s="4"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="J31" s="4"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="J32" s="4"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="J69" s="4"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="J70" s="4"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="J71" s="4"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="J72" s="4"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="J73" s="4"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
       <c r="J74" s="4"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="J75" s="4"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="J76" s="4"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="J77" s="4"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="J78" s="4"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="J79" s="4"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="J80" s="4"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="J81" s="4"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="J82" s="4"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="J83" s="4"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="J84" s="4"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="J85" s="4"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
       <c r="J86" s="4"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="J87" s="4"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="J88" s="4"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="J89" s="4"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="J90" s="4"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="J91" s="4"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="J92" s="4"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B93" s="4"/>
       <c r="J93" s="4"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.15">
       <c r="J94" s="4"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.15">
       <c r="J95" s="4"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.15">
       <c r="J96" s="4"/>
     </row>
-    <row r="97" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="10:10" x14ac:dyDescent="0.15">
       <c r="J97" s="4"/>
     </row>
-    <row r="98" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="10:10" x14ac:dyDescent="0.15">
       <c r="J98" s="4"/>
     </row>
-    <row r="99" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="10:10" x14ac:dyDescent="0.15">
       <c r="J99" s="4"/>
     </row>
-    <row r="100" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="10:10" x14ac:dyDescent="0.15">
       <c r="J100" s="4"/>
     </row>
-    <row r="101" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="10:10" x14ac:dyDescent="0.15">
       <c r="J101" s="4"/>
     </row>
-    <row r="102" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="10:10" x14ac:dyDescent="0.15">
       <c r="J102" s="4"/>
     </row>
   </sheetData>
